--- a/output/pdf_financials_xlsx/FTZ.xlsx
+++ b/output/pdf_financials_xlsx/FTZ.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5.3e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000196</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000194</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001449</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008652999999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.027391</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.027738</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.113738</v>
       </c>
     </row>
     <row r="13">
@@ -1576,40 +1576,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.468769</v>
+        <v>-0.468785</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.187139</v>
+        <v>-0.187192</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.50487</v>
+        <v>-0.505066</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.594446</v>
+        <v>-0.5946399999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.796196</v>
+        <v>-1.796263</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.333243</v>
+        <v>-0.333249</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.063085</v>
+        <v>0.063079</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.133521</v>
+        <v>-3.13497</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.216366</v>
+        <v>-1.225019</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.066732</v>
+        <v>-5.094123</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.690901</v>
+        <v>-1.718639</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.339793</v>
+        <v>-4.453531</v>
       </c>
     </row>
     <row r="28">
@@ -1662,40 +1662,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.468769</v>
+        <v>-0.468785</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.187139</v>
+        <v>-0.187192</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.50487</v>
+        <v>-0.505066</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.594446</v>
+        <v>-0.5946399999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.796196</v>
+        <v>-1.796263</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.333243</v>
+        <v>-0.333249</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.063085</v>
+        <v>0.063079</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.133521</v>
+        <v>-3.13497</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.216366</v>
+        <v>-1.225019</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.066732</v>
+        <v>-5.094123</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.690901</v>
+        <v>-1.718639</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.339793</v>
+        <v>-4.453531</v>
       </c>
     </row>
     <row r="30">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.020991</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.019325</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011169</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.026364</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002866</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001795</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>7.9e-05</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.147334</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.980579</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.221462</v>
@@ -1975,31 +1975,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.020991</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.019325</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011169</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.026364</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.002866</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001795</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>7.9e-05</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.147334</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.980579</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.221462</v>
@@ -2491,31 +2491,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.04645</v>
+        <v>0.025459</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.019325</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.011169</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.07327400000000001</v>
+        <v>0.04691</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.002866</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001795</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>7.9e-05</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.296831</v>
+        <v>0.149497</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.980579</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -6860,7 +6860,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -8414,7 +8418,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -12854,7 +12858,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -13292,7 +13300,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -17264,7 +17276,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -19816,7 +19828,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">

--- a/output/pdf_financials_xlsx/FTZ.xlsx
+++ b/output/pdf_financials_xlsx/FTZ.xlsx
@@ -11536,7 +11536,11 @@
           <t>Shares issued - private placement</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
